--- a/tests/fixtures/horarios.xlsx
+++ b/tests/fixtures/horarios.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
   <si>
     <t>Semestre</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Correo docente</t>
   </si>
   <si>
+    <t>NRC</t>
+  </si>
+  <si>
     <t>Lunes</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>lparedes@ute.edu.ec</t>
   </si>
   <si>
+    <t>1001</t>
+  </si>
+  <si>
     <t>Martes</t>
   </si>
   <si>
@@ -49,6 +55,9 @@
     <t>mcobo@ute.edu.ec</t>
   </si>
   <si>
+    <t>1002</t>
+  </si>
+  <si>
     <t>Miércoles</t>
   </si>
   <si>
@@ -58,6 +67,9 @@
     <t>jtapia@ute.edu.ec</t>
   </si>
   <si>
+    <t>1003</t>
+  </si>
+  <si>
     <t>Jueves</t>
   </si>
   <si>
@@ -67,49 +79,85 @@
     <t>rguerrero@ute.edu.ec</t>
   </si>
   <si>
+    <t>1004</t>
+  </si>
+  <si>
     <t>Viernes</t>
   </si>
   <si>
     <t>Inglés I</t>
   </si>
   <si>
+    <t>1005</t>
+  </si>
+  <si>
     <t>Patrimonio Cultural</t>
   </si>
   <si>
+    <t>1006</t>
+  </si>
+  <si>
     <t>Investigación</t>
   </si>
   <si>
     <t>svillacis@ute.edu.ec</t>
   </si>
   <si>
+    <t>1007</t>
+  </si>
+  <si>
     <t>Servicio de A&amp;B</t>
   </si>
   <si>
     <t>pmena@ute.edu.ec</t>
   </si>
   <si>
+    <t>1008</t>
+  </si>
+  <si>
     <t>Inglés II</t>
   </si>
   <si>
+    <t>1009</t>
+  </si>
+  <si>
     <t>Nutrición</t>
   </si>
   <si>
+    <t>1010</t>
+  </si>
+  <si>
     <t>Gestión de Eventos</t>
   </si>
   <si>
     <t>avallejo@ute.edu.ec</t>
   </si>
   <si>
+    <t>1011</t>
+  </si>
+  <si>
     <t>Cultura Gastronómica</t>
   </si>
   <si>
+    <t>1012</t>
+  </si>
+  <si>
     <t>Protocolo y Etiqueta</t>
   </si>
   <si>
+    <t>1013</t>
+  </si>
+  <si>
     <t>Turismo Cultural</t>
   </si>
   <si>
+    <t>1014</t>
+  </si>
+  <si>
     <t>Marketing Turístico</t>
+  </si>
+  <si>
+    <t>1015</t>
   </si>
 </sst>
 </file>
@@ -490,10 +538,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,13 +560,16 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>0.2916666666666667</v>
@@ -527,18 +578,21 @@
         <v>0.375</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>0.4166666666666667</v>
@@ -547,18 +601,21 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>0.375</v>
@@ -567,18 +624,21 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
         <v>0.625</v>
@@ -587,18 +647,21 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>0.4166666666666667</v>
@@ -607,18 +670,21 @@
         <v>0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>0.4166666666666667</v>
@@ -627,18 +693,21 @@
         <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>0.3333333333333333</v>
@@ -647,18 +716,21 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>0.5833333333333334</v>
@@ -667,18 +739,21 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
         <v>0.3333333333333333</v>
@@ -687,18 +762,21 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1">
         <v>0.625</v>
@@ -707,18 +785,21 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
         <v>0.3333333333333333</v>
@@ -727,18 +808,21 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1">
         <v>0.5833333333333334</v>
@@ -747,18 +831,21 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1">
         <v>0.4166666666666667</v>
@@ -767,18 +854,21 @@
         <v>0.5</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
         <v>0.375</v>
@@ -787,18 +877,21 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
         <v>0.3333333333333333</v>
@@ -807,10 +900,13 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
